--- a/SGC-CKN/Excel/edae2014-f5c4-481e-8465-8d244d73c8f8_Đại_trà_P377-SA_D1200_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/edae2014-f5c4-481e-8465-8d244d73c8f8_Đại_trà_P377-SA_D1200_28-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P377-SA</t>
+    <t>P377</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
